--- a/output/ARKF/00_Starter_Residual_2.5_to_5pct/ARKF_starter_residual_analysis.xlsx
+++ b/output/ARKF/00_Starter_Residual_2.5_to_5pct/ARKF_starter_residual_analysis.xlsx
@@ -525,40 +525,40 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>650.3333333333334</v>
+        <v>753</v>
       </c>
       <c r="H2" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
         <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>86.1271676300578</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="M2" t="n">
-        <v>108.3988439306358</v>
+        <v>111.4171428571429</v>
       </c>
       <c r="N2" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>280</v>
+        <v>668.1</v>
       </c>
     </row>
   </sheetData>
@@ -663,7 +663,7 @@
         <v>5.271081140864417</v>
       </c>
       <c r="E3" t="n">
-        <v>1.719020876401431</v>
+        <v>1.571556573867646</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>7.069880217628392</v>
       </c>
       <c r="E4" t="n">
-        <v>4.687119339925775</v>
+        <v>4.674289636839031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -723,18 +723,18 @@
         <v>4.66476392428682</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.5698075261183925</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Still Small</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>939</v>
+        <v>2437</v>
       </c>
       <c r="H5" t="n">
-        <v>939</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="6">
@@ -783,7 +783,7 @@
         <v>8.525880034223224</v>
       </c>
       <c r="E7" t="n">
-        <v>3.724042079262133</v>
+        <v>3.979064394301959</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>3.7496787649484</v>
       </c>
       <c r="E13" t="n">
-        <v>1.287732591107519</v>
+        <v>1.279638415514854</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2395</v>
+        <v>2437</v>
       </c>
       <c r="H13" t="n">
-        <v>2395</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="14">
@@ -993,7 +993,7 @@
         <v>5.669465567972425</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8493289320935251</v>
+        <v>0.8537684856989868</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>6.609626940393729</v>
       </c>
       <c r="E16" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I174"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1348,7 +1348,7 @@
         <v>5.513737850990946</v>
       </c>
       <c r="G8" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>5.513737850990946</v>
       </c>
       <c r="G9" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>5.513737850990946</v>
       </c>
       <c r="G10" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>5.513737850990946</v>
       </c>
       <c r="G11" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>5.513737850990946</v>
       </c>
       <c r="G12" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>5.513737850990946</v>
       </c>
       <c r="G13" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>5.511564650052159</v>
       </c>
       <c r="G14" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>5.341143532815717</v>
       </c>
       <c r="G15" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>5.177778525121754</v>
       </c>
       <c r="G16" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>5.177778525121754</v>
       </c>
       <c r="G17" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>5.146783791366811</v>
       </c>
       <c r="G18" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>4.826771092950814</v>
       </c>
       <c r="G19" t="n">
-        <v>2.374343964022382</v>
+        <v>2.264681820364429</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>493</v>
+        <v>535</v>
       </c>
     </row>
     <row r="20">
@@ -1744,7 +1744,7 @@
         <v>4.940180781888697</v>
       </c>
       <c r="G20" t="n">
-        <v>1.719020876401431</v>
+        <v>1.571556573867646</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1984</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="21">
@@ -1777,7 +1777,7 @@
         <v>7.069880217628392</v>
       </c>
       <c r="G21" t="n">
-        <v>4.687119339925775</v>
+        <v>4.674289636839031</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>7.069880217628392</v>
       </c>
       <c r="G22" t="n">
-        <v>4.687119339925775</v>
+        <v>4.674289636839031</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>7.069880217628392</v>
       </c>
       <c r="G23" t="n">
-        <v>4.687119339925775</v>
+        <v>4.674289636839031</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>7.069880217628392</v>
       </c>
       <c r="G24" t="n">
-        <v>4.687119339925775</v>
+        <v>4.674289636839031</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>4.961248124104698</v>
       </c>
       <c r="G25" t="n">
-        <v>4.687119339925775</v>
+        <v>4.674289636839031</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26">
@@ -1942,7 +1942,7 @@
         <v>14.89901692603546</v>
       </c>
       <c r="G26" t="n">
-        <v>6.308591543797745</v>
+        <v>7.358811195222178</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>14.89901692603546</v>
       </c>
       <c r="G27" t="n">
-        <v>6.308591543797745</v>
+        <v>7.358811195222178</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>14.89901692603546</v>
       </c>
       <c r="G28" t="n">
-        <v>6.308591543797745</v>
+        <v>7.358811195222178</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>14.89901692603546</v>
       </c>
       <c r="G29" t="n">
-        <v>6.308591543797745</v>
+        <v>7.358811195222178</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>4.824173450498572</v>
       </c>
       <c r="G30" t="n">
-        <v>3.724042079262133</v>
+        <v>3.979064394301959</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31">
@@ -2095,19 +2095,19 @@
         <v>44792</v>
       </c>
       <c r="C31" t="n">
-        <v>100</v>
+        <v>5.143167654047407</v>
       </c>
       <c r="D31" t="n">
         <v>4.970872373842119</v>
       </c>
       <c r="E31" t="n">
-        <v>95.02912762615789</v>
+        <v>0.1722952802052884</v>
       </c>
       <c r="F31" t="n">
         <v>8.032132497172121</v>
       </c>
       <c r="G31" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2128,19 +2128,19 @@
         <v>44827</v>
       </c>
       <c r="C32" t="n">
-        <v>100</v>
+        <v>5.413396123599439</v>
       </c>
       <c r="D32" t="n">
         <v>4.936816550273911</v>
       </c>
       <c r="E32" t="n">
-        <v>95.06318344972608</v>
+        <v>0.4765795733255276</v>
       </c>
       <c r="F32" t="n">
         <v>8.032132497172121</v>
       </c>
       <c r="G32" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2161,19 +2161,19 @@
         <v>44837</v>
       </c>
       <c r="C33" t="n">
-        <v>100</v>
+        <v>5.413396123599439</v>
       </c>
       <c r="D33" t="n">
         <v>4.932141491978562</v>
       </c>
       <c r="E33" t="n">
-        <v>95.06785850802144</v>
+        <v>0.4812546316208772</v>
       </c>
       <c r="F33" t="n">
         <v>8.032132497172121</v>
       </c>
       <c r="G33" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2194,19 +2194,19 @@
         <v>44845</v>
       </c>
       <c r="C34" t="n">
-        <v>100</v>
+        <v>5.413396123599439</v>
       </c>
       <c r="D34" t="n">
         <v>4.621854199809938</v>
       </c>
       <c r="E34" t="n">
-        <v>95.37814580019005</v>
+        <v>0.7915419237895005</v>
       </c>
       <c r="F34" t="n">
         <v>8.032132497172121</v>
       </c>
       <c r="G34" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2227,19 +2227,19 @@
         <v>44869</v>
       </c>
       <c r="C35" t="n">
-        <v>100</v>
+        <v>5.413396123599439</v>
       </c>
       <c r="D35" t="n">
         <v>4.989939360416806</v>
       </c>
       <c r="E35" t="n">
-        <v>95.01006063958319</v>
+        <v>0.4234567631826325</v>
       </c>
       <c r="F35" t="n">
         <v>8.032132497172121</v>
       </c>
       <c r="G35" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2260,19 +2260,19 @@
         <v>44894</v>
       </c>
       <c r="C36" t="n">
-        <v>100</v>
+        <v>5.413396123599439</v>
       </c>
       <c r="D36" t="n">
         <v>4.919671641311297</v>
       </c>
       <c r="E36" t="n">
-        <v>95.0803283586887</v>
+        <v>0.4937244822881421</v>
       </c>
       <c r="F36" t="n">
         <v>8.032132497172121</v>
       </c>
       <c r="G36" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2293,19 +2293,19 @@
         <v>44967</v>
       </c>
       <c r="C37" t="n">
-        <v>100</v>
+        <v>5.413396123599439</v>
       </c>
       <c r="D37" t="n">
         <v>4.970160795727135</v>
       </c>
       <c r="E37" t="n">
-        <v>95.02983920427286</v>
+        <v>0.443235327872304</v>
       </c>
       <c r="F37" t="n">
         <v>8.032132497172121</v>
       </c>
       <c r="G37" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2326,19 +2326,19 @@
         <v>45516</v>
       </c>
       <c r="C38" t="n">
-        <v>100</v>
+        <v>8.032132497172121</v>
       </c>
       <c r="D38" t="n">
         <v>4.939462425561141</v>
       </c>
       <c r="E38" t="n">
-        <v>95.06053757443885</v>
+        <v>3.09267007161098</v>
       </c>
       <c r="F38" t="n">
         <v>5.882565333475342</v>
       </c>
       <c r="G38" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>45587</v>
       </c>
       <c r="C39" t="n">
-        <v>100</v>
+        <v>8.032132497172121</v>
       </c>
       <c r="D39" t="n">
         <v>4.97041262123265</v>
       </c>
       <c r="E39" t="n">
-        <v>95.02958737876735</v>
+        <v>3.061719875939471</v>
       </c>
       <c r="F39" t="n">
         <v>5.053376782668622</v>
       </c>
       <c r="G39" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2392,19 +2392,19 @@
         <v>45590</v>
       </c>
       <c r="C40" t="n">
-        <v>100</v>
+        <v>8.032132497172121</v>
       </c>
       <c r="D40" t="n">
         <v>4.959148931330598</v>
       </c>
       <c r="E40" t="n">
-        <v>95.0408510686694</v>
+        <v>3.072983565841523</v>
       </c>
       <c r="F40" t="n">
         <v>4.959148931330598</v>
       </c>
       <c r="G40" t="n">
-        <v>2.198252955153464</v>
+        <v>1.574645848741667</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>308</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41">
@@ -2437,7 +2437,7 @@
         <v>6.174456053035262</v>
       </c>
       <c r="G41" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>6.174456053035262</v>
       </c>
       <c r="G42" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>6.174456053035262</v>
       </c>
       <c r="G43" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>6.174456053035262</v>
       </c>
       <c r="G44" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>5.728735364110522</v>
       </c>
       <c r="G45" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>5.728735364110522</v>
       </c>
       <c r="G46" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>5.728735364110522</v>
       </c>
       <c r="G47" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>5.728735364110522</v>
       </c>
       <c r="G48" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>5.728735364110522</v>
       </c>
       <c r="G49" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>5.728735364110522</v>
       </c>
       <c r="G50" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>4.68884771881706</v>
       </c>
       <c r="G51" t="n">
-        <v>1.105259630764662</v>
+        <v>1.007297972424495</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2775,40 +2775,40 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>960</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GLBE US Equity</t>
+          <t>FTOXX US Equity</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45117</v>
+        <v>45915</v>
       </c>
       <c r="C52" t="n">
-        <v>5.020042191072747</v>
+        <v>5.18211727045122</v>
       </c>
       <c r="D52" t="n">
-        <v>4.901471824650921</v>
+        <v>3.688200651123445</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1185703664218263</v>
+        <v>1.493916619327774</v>
       </c>
       <c r="F52" t="n">
-        <v>5.064178137113904</v>
+        <v>3.688200651123445</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9980327726384945</v>
+        <v>0.1914413833558123</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53">
@@ -2818,22 +2818,22 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45196</v>
+        <v>45117</v>
       </c>
       <c r="C53" t="n">
-        <v>5.035821170514549</v>
+        <v>5.020042191072747</v>
       </c>
       <c r="D53" t="n">
-        <v>4.924628619113782</v>
+        <v>4.901471824650921</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1111925514007677</v>
+        <v>0.1185703664218263</v>
       </c>
       <c r="F53" t="n">
         <v>5.064178137113904</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9980327726384945</v>
+        <v>0.9447343673179117</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54">
@@ -2851,22 +2851,22 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45202</v>
+        <v>45196</v>
       </c>
       <c r="C54" t="n">
         <v>5.035821170514549</v>
       </c>
       <c r="D54" t="n">
-        <v>4.998182631228062</v>
+        <v>4.924628619113782</v>
       </c>
       <c r="E54" t="n">
-        <v>0.03763853928648775</v>
+        <v>0.1111925514007677</v>
       </c>
       <c r="F54" t="n">
         <v>5.064178137113904</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9980327726384945</v>
+        <v>0.9447343673179117</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -2884,63 +2884,63 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45209</v>
+        <v>45202</v>
       </c>
       <c r="C55" t="n">
+        <v>5.035821170514549</v>
+      </c>
+      <c r="D55" t="n">
+        <v>4.998182631228062</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.03763853928648775</v>
+      </c>
+      <c r="F55" t="n">
         <v>5.064178137113904</v>
       </c>
-      <c r="D55" t="n">
-        <v>4.753399014279951</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.3107791228339529</v>
-      </c>
-      <c r="F55" t="n">
-        <v>4.767229385481597</v>
-      </c>
       <c r="G55" t="n">
-        <v>0.9980327726384945</v>
+        <v>0.9447343673179117</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>689</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HOOD US Equity</t>
+          <t>GLBE US Equity</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>44720</v>
+        <v>45209</v>
       </c>
       <c r="C56" t="n">
-        <v>5.933071795518035</v>
+        <v>5.064178137113904</v>
       </c>
       <c r="D56" t="n">
-        <v>4.711289437211587</v>
+        <v>4.753399014279951</v>
       </c>
       <c r="E56" t="n">
-        <v>1.221782358306448</v>
+        <v>0.3107791228339529</v>
       </c>
       <c r="F56" t="n">
-        <v>9.573358807283071</v>
+        <v>4.767229385481597</v>
       </c>
       <c r="G56" t="n">
-        <v>7.031976110151669</v>
+        <v>0.9447343673179117</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>731</v>
       </c>
     </row>
     <row r="57">
@@ -2950,22 +2950,22 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>44741</v>
+        <v>44720</v>
       </c>
       <c r="C57" t="n">
         <v>5.933071795518035</v>
       </c>
       <c r="D57" t="n">
-        <v>2.899371991254138</v>
+        <v>4.711289437211587</v>
       </c>
       <c r="E57" t="n">
-        <v>3.033699804263896</v>
+        <v>1.221782358306448</v>
       </c>
       <c r="F57" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G57" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -2983,22 +2983,22 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>44774</v>
+        <v>44741</v>
       </c>
       <c r="C58" t="n">
         <v>5.933071795518035</v>
       </c>
       <c r="D58" t="n">
-        <v>4.85793210339704</v>
+        <v>2.899371991254138</v>
       </c>
       <c r="E58" t="n">
-        <v>1.075139692120994</v>
+        <v>3.033699804263896</v>
       </c>
       <c r="F58" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G58" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>44781</v>
+        <v>44774</v>
       </c>
       <c r="C59" t="n">
         <v>5.933071795518035</v>
       </c>
       <c r="D59" t="n">
-        <v>4.913233906858792</v>
+        <v>4.85793210339704</v>
       </c>
       <c r="E59" t="n">
-        <v>1.019837888659243</v>
+        <v>1.075139692120994</v>
       </c>
       <c r="F59" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G59" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -3049,22 +3049,22 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>44791</v>
+        <v>44781</v>
       </c>
       <c r="C60" t="n">
         <v>5.933071795518035</v>
       </c>
       <c r="D60" t="n">
-        <v>4.997467321364778</v>
+        <v>4.913233906858792</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9356044741532568</v>
+        <v>1.019837888659243</v>
       </c>
       <c r="F60" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G60" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -3082,22 +3082,22 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>44916</v>
+        <v>44791</v>
       </c>
       <c r="C61" t="n">
-        <v>7.641983708602041</v>
+        <v>5.933071795518035</v>
       </c>
       <c r="D61" t="n">
-        <v>4.968405183561899</v>
+        <v>4.997467321364778</v>
       </c>
       <c r="E61" t="n">
-        <v>2.673578525040142</v>
+        <v>0.9356044741532568</v>
       </c>
       <c r="F61" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G61" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62">
@@ -3115,22 +3115,22 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>44938</v>
+        <v>44916</v>
       </c>
       <c r="C62" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D62" t="n">
-        <v>4.950838955042576</v>
+        <v>4.968405183561899</v>
       </c>
       <c r="E62" t="n">
-        <v>2.691144753559465</v>
+        <v>2.673578525040142</v>
       </c>
       <c r="F62" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G62" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
@@ -3148,22 +3148,22 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>44944</v>
+        <v>44938</v>
       </c>
       <c r="C63" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D63" t="n">
-        <v>4.98038100022369</v>
+        <v>4.950838955042576</v>
       </c>
       <c r="E63" t="n">
-        <v>2.661602708378351</v>
+        <v>2.691144753559465</v>
       </c>
       <c r="F63" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G63" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -3181,22 +3181,22 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>44972</v>
+        <v>44944</v>
       </c>
       <c r="C64" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D64" t="n">
-        <v>4.969288271320749</v>
+        <v>4.98038100022369</v>
       </c>
       <c r="E64" t="n">
-        <v>2.672695437281292</v>
+        <v>2.661602708378351</v>
       </c>
       <c r="F64" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G64" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -3214,22 +3214,22 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>44984</v>
+        <v>44972</v>
       </c>
       <c r="C65" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D65" t="n">
-        <v>4.975846772038326</v>
+        <v>4.969288271320749</v>
       </c>
       <c r="E65" t="n">
-        <v>2.666136936563714</v>
+        <v>2.672695437281292</v>
       </c>
       <c r="F65" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G65" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -3247,22 +3247,22 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>44988</v>
+        <v>44984</v>
       </c>
       <c r="C66" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D66" t="n">
-        <v>4.890670482916393</v>
+        <v>4.975846772038326</v>
       </c>
       <c r="E66" t="n">
-        <v>2.751313225685648</v>
+        <v>2.666136936563714</v>
       </c>
       <c r="F66" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G66" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -3280,22 +3280,22 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45028</v>
+        <v>44988</v>
       </c>
       <c r="C67" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D67" t="n">
-        <v>4.959326261836294</v>
+        <v>4.890670482916393</v>
       </c>
       <c r="E67" t="n">
-        <v>2.682657446765747</v>
+        <v>2.751313225685648</v>
       </c>
       <c r="F67" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G67" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68">
@@ -3313,22 +3313,22 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45030</v>
+        <v>45028</v>
       </c>
       <c r="C68" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D68" t="n">
-        <v>4.983148659841421</v>
+        <v>4.959326261836294</v>
       </c>
       <c r="E68" t="n">
-        <v>2.65883504876062</v>
+        <v>2.682657446765747</v>
       </c>
       <c r="F68" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G68" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3346,22 +3346,22 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45139</v>
+        <v>45030</v>
       </c>
       <c r="C69" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D69" t="n">
-        <v>4.917796567128436</v>
+        <v>4.983148659841421</v>
       </c>
       <c r="E69" t="n">
-        <v>2.724187141473605</v>
+        <v>2.65883504876062</v>
       </c>
       <c r="F69" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G69" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70">
@@ -3379,22 +3379,22 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45142</v>
+        <v>45139</v>
       </c>
       <c r="C70" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D70" t="n">
-        <v>4.818875672162045</v>
+        <v>4.917796567128436</v>
       </c>
       <c r="E70" t="n">
-        <v>2.823108036439995</v>
+        <v>2.724187141473605</v>
       </c>
       <c r="F70" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G70" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -3412,22 +3412,22 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>45169</v>
+        <v>45142</v>
       </c>
       <c r="C71" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D71" t="n">
-        <v>4.991595618865946</v>
+        <v>4.818875672162045</v>
       </c>
       <c r="E71" t="n">
-        <v>2.650388089736095</v>
+        <v>2.823108036439995</v>
       </c>
       <c r="F71" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G71" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72">
@@ -3445,22 +3445,22 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45211</v>
+        <v>45169</v>
       </c>
       <c r="C72" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D72" t="n">
-        <v>4.925827275918071</v>
+        <v>4.991595618865946</v>
       </c>
       <c r="E72" t="n">
-        <v>2.716156432683969</v>
+        <v>2.650388089736095</v>
       </c>
       <c r="F72" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G72" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
@@ -3478,22 +3478,22 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45229</v>
+        <v>45211</v>
       </c>
       <c r="C73" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D73" t="n">
-        <v>4.8891353788252</v>
+        <v>4.925827275918071</v>
       </c>
       <c r="E73" t="n">
-        <v>2.752848329776841</v>
+        <v>2.716156432683969</v>
       </c>
       <c r="F73" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G73" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>375</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
@@ -3511,22 +3511,22 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45607</v>
+        <v>45229</v>
       </c>
       <c r="C74" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D74" t="n">
-        <v>4.925114419121633</v>
+        <v>4.8891353788252</v>
       </c>
       <c r="E74" t="n">
-        <v>2.716869289480408</v>
+        <v>2.752848329776841</v>
       </c>
       <c r="F74" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G74" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8</v>
+        <v>375</v>
       </c>
     </row>
     <row r="75">
@@ -3544,22 +3544,22 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45616</v>
+        <v>45607</v>
       </c>
       <c r="C75" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D75" t="n">
-        <v>4.996564234799495</v>
+        <v>4.925114419121633</v>
       </c>
       <c r="E75" t="n">
-        <v>2.645419473802546</v>
+        <v>2.716869289480408</v>
       </c>
       <c r="F75" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G75" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
@@ -3577,22 +3577,22 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>45618</v>
+        <v>45616</v>
       </c>
       <c r="C76" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D76" t="n">
-        <v>4.957335102631617</v>
+        <v>4.996564234799495</v>
       </c>
       <c r="E76" t="n">
-        <v>2.684648605970423</v>
+        <v>2.645419473802546</v>
       </c>
       <c r="F76" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G76" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -3610,22 +3610,22 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>45638</v>
+        <v>45618</v>
       </c>
       <c r="C77" t="n">
         <v>7.641983708602041</v>
       </c>
       <c r="D77" t="n">
-        <v>4.997114062237892</v>
+        <v>4.957335102631617</v>
       </c>
       <c r="E77" t="n">
-        <v>2.644869646364149</v>
+        <v>2.684648605970423</v>
       </c>
       <c r="F77" t="n">
         <v>9.573358807283071</v>
       </c>
       <c r="G77" t="n">
-        <v>7.031976110151669</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3633,32 +3633,32 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MELI US Equity</t>
+          <t>HOOD US Equity</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>43914</v>
+        <v>45638</v>
       </c>
       <c r="C78" t="n">
-        <v>5.524905904616847</v>
+        <v>7.641983708602041</v>
       </c>
       <c r="D78" t="n">
-        <v>4.906580455490387</v>
+        <v>4.997114062237892</v>
       </c>
       <c r="E78" t="n">
-        <v>0.61832544912646</v>
+        <v>2.644869646364149</v>
       </c>
       <c r="F78" t="n">
-        <v>7.382968998402578</v>
+        <v>9.573358807283071</v>
       </c>
       <c r="G78" t="n">
-        <v>2.773306416837073</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3666,32 +3666,32 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MELI US Equity</t>
+          <t>HOOD US Equity</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>43945</v>
+        <v>45912</v>
       </c>
       <c r="C79" t="n">
-        <v>5.524905904616847</v>
+        <v>9.573358807283071</v>
       </c>
       <c r="D79" t="n">
-        <v>4.833068729203252</v>
+        <v>4.995687382795512</v>
       </c>
       <c r="E79" t="n">
-        <v>0.6918371754135944</v>
+        <v>4.577671424487559</v>
       </c>
       <c r="F79" t="n">
-        <v>7.382968998402578</v>
+        <v>6.03416353193025</v>
       </c>
       <c r="G79" t="n">
-        <v>2.773306416837073</v>
+        <v>5.963798767672147</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
@@ -3709,22 +3709,22 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>43950</v>
+        <v>43914</v>
       </c>
       <c r="C80" t="n">
         <v>5.524905904616847</v>
       </c>
       <c r="D80" t="n">
-        <v>4.876787058968265</v>
+        <v>4.906580455490387</v>
       </c>
       <c r="E80" t="n">
-        <v>0.6481188456485816</v>
+        <v>0.61832544912646</v>
       </c>
       <c r="F80" t="n">
         <v>7.382968998402578</v>
       </c>
       <c r="G80" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -3742,22 +3742,22 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>43955</v>
+        <v>43945</v>
       </c>
       <c r="C81" t="n">
         <v>5.524905904616847</v>
       </c>
       <c r="D81" t="n">
-        <v>4.778725274631993</v>
+        <v>4.833068729203252</v>
       </c>
       <c r="E81" t="n">
-        <v>0.7461806299848535</v>
+        <v>0.6918371754135944</v>
       </c>
       <c r="F81" t="n">
         <v>7.382968998402578</v>
       </c>
       <c r="G81" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -3775,22 +3775,22 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>44070</v>
+        <v>43950</v>
       </c>
       <c r="C82" t="n">
-        <v>5.815401712843047</v>
+        <v>5.524905904616847</v>
       </c>
       <c r="D82" t="n">
-        <v>4.959208161932572</v>
+        <v>4.876787058968265</v>
       </c>
       <c r="E82" t="n">
-        <v>0.8561935509104757</v>
+        <v>0.6481188456485816</v>
       </c>
       <c r="F82" t="n">
         <v>7.382968998402578</v>
       </c>
       <c r="G82" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -3808,22 +3808,22 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>44134</v>
+        <v>43955</v>
       </c>
       <c r="C83" t="n">
-        <v>5.815401712843047</v>
+        <v>5.524905904616847</v>
       </c>
       <c r="D83" t="n">
-        <v>4.931603375009734</v>
+        <v>4.778725274631993</v>
       </c>
       <c r="E83" t="n">
-        <v>0.883798337833313</v>
+        <v>0.7461806299848535</v>
       </c>
       <c r="F83" t="n">
         <v>7.382968998402578</v>
       </c>
       <c r="G83" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -3841,22 +3841,22 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>44144</v>
+        <v>44070</v>
       </c>
       <c r="C84" t="n">
         <v>5.815401712843047</v>
       </c>
       <c r="D84" t="n">
-        <v>4.832389695518676</v>
+        <v>4.959208161932572</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9830120173243708</v>
+        <v>0.8561935509104757</v>
       </c>
       <c r="F84" t="n">
         <v>7.382968998402578</v>
       </c>
       <c r="G84" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>515</v>
+        <v>53</v>
       </c>
     </row>
     <row r="85">
@@ -3874,22 +3874,22 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>44663</v>
+        <v>44134</v>
       </c>
       <c r="C85" t="n">
         <v>5.815401712843047</v>
       </c>
       <c r="D85" t="n">
-        <v>4.977659119450513</v>
+        <v>4.931603375009734</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8377425933925347</v>
+        <v>0.883798337833313</v>
       </c>
       <c r="F85" t="n">
         <v>7.382968998402578</v>
       </c>
       <c r="G85" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -3907,22 +3907,22 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>44676</v>
+        <v>44144</v>
       </c>
       <c r="C86" t="n">
         <v>5.815401712843047</v>
       </c>
       <c r="D86" t="n">
-        <v>4.998865496705503</v>
+        <v>4.832389695518676</v>
       </c>
       <c r="E86" t="n">
-        <v>0.8165362161375445</v>
+        <v>0.9830120173243708</v>
       </c>
       <c r="F86" t="n">
         <v>7.382968998402578</v>
       </c>
       <c r="G86" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>515</v>
       </c>
     </row>
     <row r="87">
@@ -3940,22 +3940,22 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>44725</v>
+        <v>44663</v>
       </c>
       <c r="C87" t="n">
         <v>5.815401712843047</v>
       </c>
       <c r="D87" t="n">
-        <v>4.992475360475862</v>
+        <v>4.977659119450513</v>
       </c>
       <c r="E87" t="n">
-        <v>0.822926352367185</v>
+        <v>0.8377425933925347</v>
       </c>
       <c r="F87" t="n">
         <v>7.382968998402578</v>
       </c>
       <c r="G87" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
@@ -3973,22 +3973,22 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>44741</v>
+        <v>44676</v>
       </c>
       <c r="C88" t="n">
         <v>5.815401712843047</v>
       </c>
       <c r="D88" t="n">
-        <v>2.719990020511092</v>
+        <v>4.998865496705503</v>
       </c>
       <c r="E88" t="n">
-        <v>3.095411692331955</v>
+        <v>0.8165362161375445</v>
       </c>
       <c r="F88" t="n">
         <v>7.382968998402578</v>
       </c>
       <c r="G88" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4006,22 +4006,22 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45054</v>
+        <v>44725</v>
       </c>
       <c r="C89" t="n">
+        <v>5.815401712843047</v>
+      </c>
+      <c r="D89" t="n">
+        <v>4.992475360475862</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.822926352367185</v>
+      </c>
+      <c r="F89" t="n">
         <v>7.382968998402578</v>
       </c>
-      <c r="D89" t="n">
-        <v>4.914640790801085</v>
-      </c>
-      <c r="E89" t="n">
-        <v>2.468328207601493</v>
-      </c>
-      <c r="F89" t="n">
-        <v>5.188106940718451</v>
-      </c>
       <c r="G89" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4039,55 +4039,55 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45070</v>
+        <v>44741</v>
       </c>
       <c r="C90" t="n">
+        <v>5.815401712843047</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2.719990020511092</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3.095411692331955</v>
+      </c>
+      <c r="F90" t="n">
         <v>7.382968998402578</v>
       </c>
-      <c r="D90" t="n">
-        <v>4.985290734810233</v>
-      </c>
-      <c r="E90" t="n">
-        <v>2.397678263592345</v>
-      </c>
-      <c r="F90" t="n">
-        <v>4.985290734810233</v>
-      </c>
       <c r="G90" t="n">
-        <v>2.773306416837073</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>828</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PATH US Equity</t>
+          <t>MELI US Equity</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>44574</v>
+        <v>45054</v>
       </c>
       <c r="C91" t="n">
-        <v>5.110962050589924</v>
+        <v>7.382968998402578</v>
       </c>
       <c r="D91" t="n">
-        <v>4.90667219956075</v>
+        <v>4.914640790801085</v>
       </c>
       <c r="E91" t="n">
-        <v>0.2042898510291744</v>
+        <v>2.468328207601493</v>
       </c>
       <c r="F91" t="n">
-        <v>7.714164468316685</v>
+        <v>5.188106940718451</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4095,40 +4095,40 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PATH US Equity</t>
+          <t>MELI US Equity</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>44651</v>
+        <v>45070</v>
       </c>
       <c r="C92" t="n">
-        <v>6.367229767352131</v>
+        <v>7.382968998402578</v>
       </c>
       <c r="D92" t="n">
-        <v>4.834114679695142</v>
+        <v>4.985290734810233</v>
       </c>
       <c r="E92" t="n">
-        <v>1.533115087656989</v>
+        <v>2.397678263592345</v>
       </c>
       <c r="F92" t="n">
-        <v>7.714164468316685</v>
+        <v>4.985290734810233</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>2.640613764228984</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>28</v>
+        <v>870</v>
       </c>
     </row>
     <row r="93">
@@ -4138,16 +4138,16 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>44685</v>
+        <v>44574</v>
       </c>
       <c r="C93" t="n">
-        <v>6.367229767352131</v>
+        <v>5.110962050589924</v>
       </c>
       <c r="D93" t="n">
-        <v>4.970661305627655</v>
+        <v>4.90667219956075</v>
       </c>
       <c r="E93" t="n">
-        <v>1.396568461724477</v>
+        <v>0.2042898510291744</v>
       </c>
       <c r="F93" t="n">
         <v>7.714164468316685</v>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
@@ -4171,16 +4171,16 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>44741</v>
+        <v>44651</v>
       </c>
       <c r="C94" t="n">
-        <v>7.702111336570387</v>
+        <v>6.367229767352131</v>
       </c>
       <c r="D94" t="n">
-        <v>3.992978904849368</v>
+        <v>4.834114679695142</v>
       </c>
       <c r="E94" t="n">
-        <v>3.709132431721019</v>
+        <v>1.533115087656989</v>
       </c>
       <c r="F94" t="n">
         <v>7.714164468316685</v>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95">
@@ -4204,19 +4204,19 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>44860</v>
+        <v>44685</v>
       </c>
       <c r="C95" t="n">
+        <v>6.367229767352131</v>
+      </c>
+      <c r="D95" t="n">
+        <v>4.970661305627655</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.396568461724477</v>
+      </c>
+      <c r="F95" t="n">
         <v>7.714164468316685</v>
-      </c>
-      <c r="D95" t="n">
-        <v>4.941020467958507</v>
-      </c>
-      <c r="E95" t="n">
-        <v>2.773144000358179</v>
-      </c>
-      <c r="F95" t="n">
-        <v>7.566439775688953</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4237,19 +4237,19 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>44896</v>
+        <v>44741</v>
       </c>
       <c r="C96" t="n">
+        <v>7.702111336570387</v>
+      </c>
+      <c r="D96" t="n">
+        <v>3.992978904849368</v>
+      </c>
+      <c r="E96" t="n">
+        <v>3.709132431721019</v>
+      </c>
+      <c r="F96" t="n">
         <v>7.714164468316685</v>
-      </c>
-      <c r="D96" t="n">
-        <v>4.98988104994086</v>
-      </c>
-      <c r="E96" t="n">
-        <v>2.724283418375825</v>
-      </c>
-      <c r="F96" t="n">
-        <v>7.566439775688953</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -4270,16 +4270,16 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45050</v>
+        <v>44860</v>
       </c>
       <c r="C97" t="n">
         <v>7.714164468316685</v>
       </c>
       <c r="D97" t="n">
-        <v>4.826313067059675</v>
+        <v>4.941020467958507</v>
       </c>
       <c r="E97" t="n">
-        <v>2.88785140125701</v>
+        <v>2.773144000358179</v>
       </c>
       <c r="F97" t="n">
         <v>7.566439775688953</v>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98">
@@ -4303,19 +4303,19 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45390</v>
+        <v>44896</v>
       </c>
       <c r="C98" t="n">
         <v>7.714164468316685</v>
       </c>
       <c r="D98" t="n">
-        <v>4.975604111027922</v>
+        <v>4.98988104994086</v>
       </c>
       <c r="E98" t="n">
-        <v>2.738560357288764</v>
+        <v>2.724283418375825</v>
       </c>
       <c r="F98" t="n">
-        <v>5.069473227187867</v>
+        <v>7.566439775688953</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -4336,19 +4336,19 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>45394</v>
+        <v>45050</v>
       </c>
       <c r="C99" t="n">
         <v>7.714164468316685</v>
       </c>
       <c r="D99" t="n">
-        <v>4.946750725013205</v>
+        <v>4.826313067059675</v>
       </c>
       <c r="E99" t="n">
-        <v>2.76741374330348</v>
+        <v>2.88785140125701</v>
       </c>
       <c r="F99" t="n">
-        <v>5.037327541103323</v>
+        <v>7.566439775688953</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
@@ -4369,19 +4369,19 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45405</v>
+        <v>45390</v>
       </c>
       <c r="C100" t="n">
         <v>7.714164468316685</v>
       </c>
       <c r="D100" t="n">
-        <v>4.749178658273565</v>
+        <v>4.975604111027922</v>
       </c>
       <c r="E100" t="n">
-        <v>2.96498581004312</v>
+        <v>2.738560357288764</v>
       </c>
       <c r="F100" t="n">
-        <v>5.037327541103323</v>
+        <v>5.069473227187867</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -4402,55 +4402,55 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45429</v>
+        <v>45394</v>
       </c>
       <c r="C101" t="n">
         <v>7.714164468316685</v>
       </c>
       <c r="D101" t="n">
-        <v>4.988475273464997</v>
+        <v>4.946750725013205</v>
       </c>
       <c r="E101" t="n">
-        <v>2.725689194851689</v>
+        <v>2.76741374330348</v>
       </c>
       <c r="F101" t="n">
-        <v>4.995331018864389</v>
+        <v>5.037327541103323</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>370</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PINS US Equity</t>
+          <t>PATH US Equity</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>44144</v>
+        <v>45405</v>
       </c>
       <c r="C102" t="n">
-        <v>5.928497681120896</v>
+        <v>7.714164468316685</v>
       </c>
       <c r="D102" t="n">
-        <v>4.981956305248669</v>
+        <v>4.749178658273565</v>
       </c>
       <c r="E102" t="n">
-        <v>0.9465413758722265</v>
+        <v>2.96498581004312</v>
       </c>
       <c r="F102" t="n">
-        <v>5.022477956931419</v>
+        <v>5.037327541103323</v>
       </c>
       <c r="G102" t="n">
-        <v>2.298359534275684</v>
+        <v>0</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4458,65 +4458,65 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PINS US Equity</t>
+          <t>PATH US Equity</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>44155</v>
+        <v>45429</v>
       </c>
       <c r="C103" t="n">
-        <v>5.928497681120896</v>
+        <v>7.714164468316685</v>
       </c>
       <c r="D103" t="n">
-        <v>4.774793493778317</v>
+        <v>4.988475273464997</v>
       </c>
       <c r="E103" t="n">
-        <v>1.153704187342579</v>
+        <v>2.725689194851689</v>
       </c>
       <c r="F103" t="n">
-        <v>4.863308526037232</v>
+        <v>4.995331018864389</v>
       </c>
       <c r="G103" t="n">
-        <v>2.298359534275684</v>
+        <v>0</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1743</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PLTR US Equity</t>
+          <t>PINS US Equity</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45764</v>
+        <v>44144</v>
       </c>
       <c r="C104" t="n">
-        <v>5.055535276933488</v>
+        <v>5.928497681120896</v>
       </c>
       <c r="D104" t="n">
-        <v>4.850765497340697</v>
+        <v>4.981956305248669</v>
       </c>
       <c r="E104" t="n">
-        <v>0.204769779592791</v>
+        <v>0.9465413758722265</v>
       </c>
       <c r="F104" t="n">
-        <v>5.561187113321099</v>
+        <v>5.022477956931419</v>
       </c>
       <c r="G104" t="n">
-        <v>3.990649944335645</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4524,32 +4524,32 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PLTR US Equity</t>
+          <t>PINS US Equity</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45784</v>
+        <v>44155</v>
       </c>
       <c r="C105" t="n">
-        <v>5.561187113321099</v>
+        <v>5.928497681120896</v>
       </c>
       <c r="D105" t="n">
-        <v>4.745455998069836</v>
+        <v>4.774793493778317</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8157311152512632</v>
+        <v>1.153704187342579</v>
       </c>
       <c r="F105" t="n">
-        <v>4.870882560480632</v>
+        <v>4.863308526037232</v>
       </c>
       <c r="G105" t="n">
-        <v>3.990649944335645</v>
+        <v>1.855638104370069</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4557,32 +4557,32 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>114</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PYPL US Equity</t>
+          <t>PLTR US Equity</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>44287</v>
+        <v>45764</v>
       </c>
       <c r="C106" t="n">
-        <v>5.669465567972425</v>
+        <v>5.055535276933488</v>
       </c>
       <c r="D106" t="n">
-        <v>4.539745426442118</v>
+        <v>4.850765497340697</v>
       </c>
       <c r="E106" t="n">
-        <v>1.129720141530307</v>
+        <v>0.204769779592791</v>
       </c>
       <c r="F106" t="n">
-        <v>5.155833063830848</v>
+        <v>5.561187113321099</v>
       </c>
       <c r="G106" t="n">
-        <v>0.8493289320935251</v>
+        <v>4.351995227361876</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4590,40 +4590,40 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>102</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PYPL US Equity</t>
+          <t>PLTR US Equity</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>44398</v>
+        <v>45784</v>
       </c>
       <c r="C107" t="n">
-        <v>5.669465567972425</v>
+        <v>5.561187113321099</v>
       </c>
       <c r="D107" t="n">
-        <v>4.985831962061393</v>
+        <v>4.745455998069836</v>
       </c>
       <c r="E107" t="n">
-        <v>0.6836336059110319</v>
+        <v>0.8157311152512632</v>
       </c>
       <c r="F107" t="n">
-        <v>5.155833063830848</v>
+        <v>4.870882560480632</v>
       </c>
       <c r="G107" t="n">
-        <v>0.8493289320935251</v>
+        <v>4.351995227361876</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
     </row>
     <row r="108">
@@ -4633,55 +4633,55 @@
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>44406</v>
+        <v>44287</v>
       </c>
       <c r="C108" t="n">
         <v>5.669465567972425</v>
       </c>
       <c r="D108" t="n">
-        <v>4.739888465289915</v>
+        <v>4.539745426442118</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9295771026825106</v>
+        <v>1.129720141530307</v>
       </c>
       <c r="F108" t="n">
-        <v>4.741084117657577</v>
+        <v>5.155833063830848</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8493289320935251</v>
+        <v>0.8537684856989868</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1492</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RBLX US Equity</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>45840</v>
+        <v>44398</v>
       </c>
       <c r="C109" t="n">
-        <v>5.613864780460612</v>
+        <v>5.669465567972425</v>
       </c>
       <c r="D109" t="n">
-        <v>4.932283529086307</v>
+        <v>4.985831962061393</v>
       </c>
       <c r="E109" t="n">
-        <v>0.6815812513743049</v>
+        <v>0.6836336059110319</v>
       </c>
       <c r="F109" t="n">
-        <v>5.516035029738209</v>
+        <v>5.155833063830848</v>
       </c>
       <c r="G109" t="n">
-        <v>4.370070549386075</v>
+        <v>0.8537684856989868</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4689,40 +4689,40 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RBLX US Equity</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>45849</v>
+        <v>44406</v>
       </c>
       <c r="C110" t="n">
-        <v>5.613864780460612</v>
+        <v>5.669465567972425</v>
       </c>
       <c r="D110" t="n">
-        <v>4.932328586351856</v>
+        <v>4.739888465289915</v>
       </c>
       <c r="E110" t="n">
-        <v>0.6815361941087561</v>
+        <v>0.9295771026825106</v>
       </c>
       <c r="F110" t="n">
-        <v>5.516035029738209</v>
+        <v>4.741084117657577</v>
       </c>
       <c r="G110" t="n">
-        <v>4.370070549386075</v>
+        <v>0.8537684856989868</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="111">
@@ -4732,22 +4732,22 @@
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>45860</v>
+        <v>45840</v>
       </c>
       <c r="C111" t="n">
         <v>5.613864780460612</v>
       </c>
       <c r="D111" t="n">
-        <v>4.988264730696161</v>
+        <v>4.932283529086307</v>
       </c>
       <c r="E111" t="n">
-        <v>0.6256000497644507</v>
+        <v>0.6815812513743049</v>
       </c>
       <c r="F111" t="n">
-        <v>5.40699844137946</v>
+        <v>5.516035029738209</v>
       </c>
       <c r="G111" t="n">
-        <v>4.370070549386075</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
@@ -4765,55 +4765,55 @@
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>45873</v>
+        <v>45849</v>
       </c>
       <c r="C112" t="n">
         <v>5.613864780460612</v>
       </c>
       <c r="D112" t="n">
-        <v>4.562096005326168</v>
+        <v>4.932328586351856</v>
       </c>
       <c r="E112" t="n">
-        <v>1.051768775134444</v>
+        <v>0.6815361941087561</v>
       </c>
       <c r="F112" t="n">
-        <v>4.562096005326168</v>
+        <v>5.516035029738209</v>
       </c>
       <c r="G112" t="n">
-        <v>4.370070549386075</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SE US Equity</t>
+          <t>RBLX US Equity</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>44341</v>
+        <v>45860</v>
       </c>
       <c r="C113" t="n">
-        <v>5.06991760420709</v>
+        <v>5.613864780460612</v>
       </c>
       <c r="D113" t="n">
-        <v>4.939008864336866</v>
+        <v>4.988264730696161</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1309087398702236</v>
+        <v>0.6256000497644507</v>
       </c>
       <c r="F113" t="n">
-        <v>5.620132363709971</v>
+        <v>5.40699844137946</v>
       </c>
       <c r="G113" t="n">
-        <v>2.207612058863048</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4821,40 +4821,40 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SE US Equity</t>
+          <t>RBLX US Equity</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>44344</v>
+        <v>45873</v>
       </c>
       <c r="C114" t="n">
-        <v>5.079875835860935</v>
+        <v>5.613864780460612</v>
       </c>
       <c r="D114" t="n">
-        <v>4.943210923606574</v>
+        <v>4.562096005326168</v>
       </c>
       <c r="E114" t="n">
-        <v>0.1366649122543606</v>
+        <v>1.051768775134444</v>
       </c>
       <c r="F114" t="n">
-        <v>5.620132363709971</v>
+        <v>4.704286363313846</v>
       </c>
       <c r="G114" t="n">
-        <v>2.207612058863048</v>
+        <v>4.003581310834871</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="115">
@@ -4864,22 +4864,22 @@
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>44362</v>
+        <v>44341</v>
       </c>
       <c r="C115" t="n">
-        <v>5.33692558964005</v>
+        <v>5.06991760420709</v>
       </c>
       <c r="D115" t="n">
-        <v>4.897044180495669</v>
+        <v>4.939008864336866</v>
       </c>
       <c r="E115" t="n">
-        <v>0.4398814091443803</v>
+        <v>0.1309087398702236</v>
       </c>
       <c r="F115" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="G115" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -4897,22 +4897,22 @@
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>44428</v>
+        <v>44344</v>
       </c>
       <c r="C116" t="n">
-        <v>5.33692558964005</v>
+        <v>5.079875835860935</v>
       </c>
       <c r="D116" t="n">
-        <v>4.961932297178255</v>
+        <v>4.943210923606574</v>
       </c>
       <c r="E116" t="n">
-        <v>0.3749932924617942</v>
+        <v>0.1366649122543606</v>
       </c>
       <c r="F116" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="G116" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -4930,22 +4930,22 @@
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>44440</v>
+        <v>44362</v>
       </c>
       <c r="C117" t="n">
         <v>5.33692558964005</v>
       </c>
       <c r="D117" t="n">
-        <v>4.888324343642531</v>
+        <v>4.897044180495669</v>
       </c>
       <c r="E117" t="n">
-        <v>0.4486012459975184</v>
+        <v>0.4398814091443803</v>
       </c>
       <c r="F117" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="G117" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="118">
@@ -4963,22 +4963,22 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>44448</v>
+        <v>44428</v>
       </c>
       <c r="C118" t="n">
         <v>5.33692558964005</v>
       </c>
       <c r="D118" t="n">
-        <v>4.752367230917907</v>
+        <v>4.961932297178255</v>
       </c>
       <c r="E118" t="n">
-        <v>0.584558358722143</v>
+        <v>0.3749932924617942</v>
       </c>
       <c r="F118" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="G118" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119">
@@ -4996,22 +4996,22 @@
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>44467</v>
+        <v>44440</v>
       </c>
       <c r="C119" t="n">
         <v>5.33692558964005</v>
       </c>
       <c r="D119" t="n">
-        <v>4.589567422864804</v>
+        <v>4.888324343642531</v>
       </c>
       <c r="E119" t="n">
-        <v>0.7473581667752454</v>
+        <v>0.4486012459975184</v>
       </c>
       <c r="F119" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="G119" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>133</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -5029,22 +5029,22 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>44606</v>
+        <v>44448</v>
       </c>
       <c r="C120" t="n">
         <v>5.33692558964005</v>
       </c>
       <c r="D120" t="n">
-        <v>4.98623256291326</v>
+        <v>4.752367230917907</v>
       </c>
       <c r="E120" t="n">
-        <v>0.3506930267267894</v>
+        <v>0.584558358722143</v>
       </c>
       <c r="F120" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="G120" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
@@ -5062,22 +5062,22 @@
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>44614</v>
+        <v>44467</v>
       </c>
       <c r="C121" t="n">
         <v>5.33692558964005</v>
       </c>
       <c r="D121" t="n">
-        <v>4.84685407064919</v>
+        <v>4.589567422864804</v>
       </c>
       <c r="E121" t="n">
-        <v>0.4900715189908595</v>
+        <v>0.7473581667752454</v>
       </c>
       <c r="F121" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="G121" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
     </row>
     <row r="122">
@@ -5095,22 +5095,22 @@
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>44622</v>
+        <v>44606</v>
       </c>
       <c r="C122" t="n">
+        <v>5.33692558964005</v>
+      </c>
+      <c r="D122" t="n">
+        <v>4.98623256291326</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.3506930267267894</v>
+      </c>
+      <c r="F122" t="n">
         <v>5.620132363709971</v>
       </c>
-      <c r="D122" t="n">
-        <v>4.98656474026411</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0.6335676234458614</v>
-      </c>
-      <c r="F122" t="n">
-        <v>5.111888512750835</v>
-      </c>
       <c r="G122" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
@@ -5128,22 +5128,22 @@
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>44645</v>
+        <v>44614</v>
       </c>
       <c r="C123" t="n">
+        <v>5.33692558964005</v>
+      </c>
+      <c r="D123" t="n">
+        <v>4.84685407064919</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4900715189908595</v>
+      </c>
+      <c r="F123" t="n">
         <v>5.620132363709971</v>
       </c>
-      <c r="D123" t="n">
-        <v>4.844089230311845</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0.7760431333981259</v>
-      </c>
-      <c r="F123" t="n">
-        <v>5.111888512750835</v>
-      </c>
       <c r="G123" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -5161,22 +5161,22 @@
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>44659</v>
+        <v>44622</v>
       </c>
       <c r="C124" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="D124" t="n">
-        <v>4.997542451115442</v>
+        <v>4.98656474026411</v>
       </c>
       <c r="E124" t="n">
-        <v>0.6225899125945293</v>
+        <v>0.6335676234458614</v>
       </c>
       <c r="F124" t="n">
-        <v>5.075937107406833</v>
+        <v>5.111888512750835</v>
       </c>
       <c r="G124" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="125">
@@ -5194,22 +5194,22 @@
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>44664</v>
+        <v>44645</v>
       </c>
       <c r="C125" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="D125" t="n">
-        <v>4.910054775609915</v>
+        <v>4.844089230311845</v>
       </c>
       <c r="E125" t="n">
-        <v>0.7100775881000567</v>
+        <v>0.7760431333981259</v>
       </c>
       <c r="F125" t="n">
-        <v>5.002535524913521</v>
+        <v>5.111888512750835</v>
       </c>
       <c r="G125" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126">
@@ -5227,55 +5227,55 @@
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>44670</v>
+        <v>44659</v>
       </c>
       <c r="C126" t="n">
         <v>5.620132363709971</v>
       </c>
       <c r="D126" t="n">
-        <v>4.872890502618961</v>
+        <v>4.997542451115442</v>
       </c>
       <c r="E126" t="n">
-        <v>0.7472418610910108</v>
+        <v>0.6225899125945293</v>
       </c>
       <c r="F126" t="n">
-        <v>4.875706103452497</v>
+        <v>5.075937107406833</v>
       </c>
       <c r="G126" t="n">
-        <v>2.207612058863048</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1228</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SICPQ US Equity</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>44273</v>
+        <v>44664</v>
       </c>
       <c r="C127" t="n">
-        <v>5.103562225949012</v>
+        <v>5.620132363709971</v>
       </c>
       <c r="D127" t="n">
-        <v>4.6949253841771</v>
+        <v>4.910054775609915</v>
       </c>
       <c r="E127" t="n">
-        <v>0.4086368417719113</v>
+        <v>0.7100775881000567</v>
       </c>
       <c r="F127" t="n">
-        <v>5.12662364125694</v>
+        <v>5.002535524913521</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -5289,34 +5289,34 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SICPQ US Equity</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>44277</v>
+        <v>44670</v>
       </c>
       <c r="C128" t="n">
-        <v>5.103562225949012</v>
+        <v>5.620132363709971</v>
       </c>
       <c r="D128" t="n">
-        <v>4.699725236929734</v>
+        <v>4.872890502618961</v>
       </c>
       <c r="E128" t="n">
-        <v>0.4038369890192781</v>
+        <v>0.7472418610910108</v>
       </c>
       <c r="F128" t="n">
-        <v>5.12662364125694</v>
+        <v>4.875706103452497</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>2.071868431170777</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>18</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="129">
@@ -5326,16 +5326,16 @@
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>44299</v>
+        <v>44273</v>
       </c>
       <c r="C129" t="n">
         <v>5.103562225949012</v>
       </c>
       <c r="D129" t="n">
-        <v>4.867480767777279</v>
+        <v>4.6949253841771</v>
       </c>
       <c r="E129" t="n">
-        <v>0.236081458171733</v>
+        <v>0.4086368417719113</v>
       </c>
       <c r="F129" t="n">
         <v>5.12662364125694</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>373</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -5359,19 +5359,19 @@
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>44677</v>
+        <v>44277</v>
       </c>
       <c r="C130" t="n">
+        <v>5.103562225949012</v>
+      </c>
+      <c r="D130" t="n">
+        <v>4.699725236929734</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.4038369890192781</v>
+      </c>
+      <c r="F130" t="n">
         <v>5.12662364125694</v>
-      </c>
-      <c r="D130" t="n">
-        <v>4.987490219120878</v>
-      </c>
-      <c r="E130" t="n">
-        <v>0.1391334221360623</v>
-      </c>
-      <c r="F130" t="n">
-        <v>5.061649986317578</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131">
@@ -5392,55 +5392,55 @@
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>44683</v>
+        <v>44299</v>
       </c>
       <c r="C131" t="n">
+        <v>5.103562225949012</v>
+      </c>
+      <c r="D131" t="n">
+        <v>4.867480767777279</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.236081458171733</v>
+      </c>
+      <c r="F131" t="n">
         <v>5.12662364125694</v>
-      </c>
-      <c r="D131" t="n">
-        <v>4.742481586423263</v>
-      </c>
-      <c r="E131" t="n">
-        <v>0.3841420548336769</v>
-      </c>
-      <c r="F131" t="n">
-        <v>4.933543046670167</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>266</v>
+        <v>373</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SOFI US Equity</t>
+          <t>SICPQ US Equity</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>45607</v>
+        <v>44677</v>
       </c>
       <c r="C132" t="n">
-        <v>5.013083861614179</v>
+        <v>5.12662364125694</v>
       </c>
       <c r="D132" t="n">
-        <v>4.949676300984551</v>
+        <v>4.987490219120878</v>
       </c>
       <c r="E132" t="n">
-        <v>0.06340756062962782</v>
+        <v>0.1391334221360623</v>
       </c>
       <c r="F132" t="n">
-        <v>5.229612458381479</v>
+        <v>5.061649986317578</v>
       </c>
       <c r="G132" t="n">
-        <v>4.218009250574899</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5448,40 +5448,40 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SOFI US Equity</t>
+          <t>SICPQ US Equity</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>45609</v>
+        <v>44683</v>
       </c>
       <c r="C133" t="n">
-        <v>5.053526818228213</v>
+        <v>5.12662364125694</v>
       </c>
       <c r="D133" t="n">
-        <v>4.840940382270133</v>
+        <v>4.742481586423263</v>
       </c>
       <c r="E133" t="n">
-        <v>0.2125864359580802</v>
+        <v>0.3841420548336769</v>
       </c>
       <c r="F133" t="n">
-        <v>5.229612458381479</v>
+        <v>4.933543046670167</v>
       </c>
       <c r="G133" t="n">
-        <v>4.218009250574899</v>
+        <v>0</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>7</v>
+        <v>266</v>
       </c>
     </row>
     <row r="134">
@@ -5491,22 +5491,22 @@
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>45622</v>
+        <v>45607</v>
       </c>
       <c r="C134" t="n">
+        <v>5.013083861614179</v>
+      </c>
+      <c r="D134" t="n">
+        <v>4.949676300984551</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.06340756062962782</v>
+      </c>
+      <c r="F134" t="n">
         <v>5.229612458381479</v>
       </c>
-      <c r="D134" t="n">
-        <v>4.525364717836497</v>
-      </c>
-      <c r="E134" t="n">
-        <v>0.7042477405449823</v>
-      </c>
-      <c r="F134" t="n">
-        <v>5.00276301869126</v>
-      </c>
       <c r="G134" t="n">
-        <v>4.218009250574899</v>
+        <v>4.284579061908301</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -5524,55 +5524,55 @@
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>45680</v>
+        <v>45609</v>
       </c>
       <c r="C135" t="n">
+        <v>5.053526818228213</v>
+      </c>
+      <c r="D135" t="n">
+        <v>4.840940382270133</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.2125864359580802</v>
+      </c>
+      <c r="F135" t="n">
         <v>5.229612458381479</v>
       </c>
-      <c r="D135" t="n">
-        <v>4.916808600430321</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0.3128038579511578</v>
-      </c>
-      <c r="F135" t="n">
-        <v>4.996045964793173</v>
-      </c>
       <c r="G135" t="n">
-        <v>4.218009250574899</v>
+        <v>4.284579061908301</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>218</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TCEHY US Equity</t>
+          <t>SOFI US Equity</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>43762</v>
+        <v>45622</v>
       </c>
       <c r="C136" t="n">
-        <v>6.721443075616359</v>
+        <v>5.229612458381479</v>
       </c>
       <c r="D136" t="n">
-        <v>4.948141874219252</v>
+        <v>4.525364717836497</v>
       </c>
       <c r="E136" t="n">
-        <v>1.773301201397107</v>
+        <v>0.7042477405449823</v>
       </c>
       <c r="F136" t="n">
-        <v>6.323999179524292</v>
+        <v>5.00276301869126</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>4.284579061908301</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -5580,40 +5580,40 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TCEHY US Equity</t>
+          <t>SOFI US Equity</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>43777</v>
+        <v>45680</v>
       </c>
       <c r="C137" t="n">
-        <v>6.721443075616359</v>
+        <v>5.229612458381479</v>
       </c>
       <c r="D137" t="n">
-        <v>4.927667817573321</v>
+        <v>4.916808600430321</v>
       </c>
       <c r="E137" t="n">
-        <v>1.793775258043039</v>
+        <v>0.3128038579511578</v>
       </c>
       <c r="F137" t="n">
-        <v>6.323999179524292</v>
+        <v>4.996045964793173</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>4.284579061908301</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4</v>
+        <v>260</v>
       </c>
     </row>
     <row r="138">
@@ -5623,16 +5623,16 @@
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>43782</v>
+        <v>43762</v>
       </c>
       <c r="C138" t="n">
         <v>6.721443075616359</v>
       </c>
       <c r="D138" t="n">
-        <v>4.763203007608267</v>
+        <v>4.948141874219252</v>
       </c>
       <c r="E138" t="n">
-        <v>1.958240068008092</v>
+        <v>1.773301201397107</v>
       </c>
       <c r="F138" t="n">
         <v>6.323999179524292</v>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139">
@@ -5656,19 +5656,19 @@
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>43958</v>
+        <v>43777</v>
       </c>
       <c r="C139" t="n">
         <v>6.721443075616359</v>
       </c>
       <c r="D139" t="n">
-        <v>4.855629172745217</v>
+        <v>4.927667817573321</v>
       </c>
       <c r="E139" t="n">
-        <v>1.865813902871142</v>
+        <v>1.793775258043039</v>
       </c>
       <c r="F139" t="n">
-        <v>5.276457214698739</v>
+        <v>6.323999179524292</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
@@ -5689,19 +5689,19 @@
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>43966</v>
+        <v>43782</v>
       </c>
       <c r="C140" t="n">
         <v>6.721443075616359</v>
       </c>
       <c r="D140" t="n">
-        <v>4.858300596811089</v>
+        <v>4.763203007608267</v>
       </c>
       <c r="E140" t="n">
-        <v>1.86314247880527</v>
+        <v>1.958240068008092</v>
       </c>
       <c r="F140" t="n">
-        <v>5.03834301060187</v>
+        <v>6.323999179524292</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>255</v>
+        <v>28</v>
       </c>
     </row>
     <row r="141">
@@ -5722,19 +5722,19 @@
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>44222</v>
+        <v>43958</v>
       </c>
       <c r="C141" t="n">
         <v>6.721443075616359</v>
       </c>
       <c r="D141" t="n">
-        <v>4.982714105091878</v>
+        <v>4.855629172745217</v>
       </c>
       <c r="E141" t="n">
-        <v>1.738728970524481</v>
+        <v>1.865813902871142</v>
       </c>
       <c r="F141" t="n">
-        <v>5.017211672659133</v>
+        <v>5.276457214698739</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
@@ -5755,55 +5755,55 @@
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>44229</v>
+        <v>43966</v>
       </c>
       <c r="C142" t="n">
         <v>6.721443075616359</v>
       </c>
       <c r="D142" t="n">
-        <v>4.900829676313351</v>
+        <v>4.858300596811089</v>
       </c>
       <c r="E142" t="n">
-        <v>1.820613399303008</v>
+        <v>1.86314247880527</v>
       </c>
       <c r="F142" t="n">
-        <v>4.900829676313351</v>
+        <v>5.03834301060187</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>363</v>
+        <v>255</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TOST US Equity</t>
+          <t>TCEHY US Equity</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>45608</v>
+        <v>44222</v>
       </c>
       <c r="C143" t="n">
-        <v>5.138629869929174</v>
+        <v>6.721443075616359</v>
       </c>
       <c r="D143" t="n">
-        <v>4.898099405636862</v>
+        <v>4.982714105091878</v>
       </c>
       <c r="E143" t="n">
-        <v>0.2405304642923118</v>
+        <v>1.738728970524481</v>
       </c>
       <c r="F143" t="n">
-        <v>5.581807858149219</v>
+        <v>5.017211672659133</v>
       </c>
       <c r="G143" t="n">
-        <v>4.579826858033617</v>
+        <v>0</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -5811,40 +5811,40 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TOST US Equity</t>
+          <t>TCEHY US Equity</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>45631</v>
+        <v>44229</v>
       </c>
       <c r="C144" t="n">
-        <v>5.342308621874411</v>
+        <v>6.721443075616359</v>
       </c>
       <c r="D144" t="n">
-        <v>4.482362597580654</v>
+        <v>4.900829676313351</v>
       </c>
       <c r="E144" t="n">
-        <v>0.8599460242937571</v>
+        <v>1.820613399303008</v>
       </c>
       <c r="F144" t="n">
-        <v>5.581807858149219</v>
+        <v>4.900829676313351</v>
       </c>
       <c r="G144" t="n">
-        <v>4.579826858033617</v>
+        <v>0</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>96</v>
+        <v>363</v>
       </c>
     </row>
     <row r="145">
@@ -5854,22 +5854,22 @@
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>45730</v>
+        <v>45608</v>
       </c>
       <c r="C145" t="n">
-        <v>5.342308621874411</v>
+        <v>5.138629869929174</v>
       </c>
       <c r="D145" t="n">
-        <v>4.987014292843731</v>
+        <v>4.898099405636862</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3552943290306798</v>
+        <v>0.2405304642923118</v>
       </c>
       <c r="F145" t="n">
         <v>5.581807858149219</v>
       </c>
       <c r="G145" t="n">
-        <v>4.579826858033617</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -5887,22 +5887,22 @@
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>45740</v>
+        <v>45631</v>
       </c>
       <c r="C146" t="n">
         <v>5.342308621874411</v>
       </c>
       <c r="D146" t="n">
-        <v>4.981228991126805</v>
+        <v>4.482362597580654</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3610796307476054</v>
+        <v>0.8599460242937571</v>
       </c>
       <c r="F146" t="n">
         <v>5.581807858149219</v>
       </c>
       <c r="G146" t="n">
-        <v>4.579826858033617</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
     </row>
     <row r="147">
@@ -5920,22 +5920,22 @@
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>45747</v>
+        <v>45730</v>
       </c>
       <c r="C147" t="n">
         <v>5.342308621874411</v>
       </c>
       <c r="D147" t="n">
-        <v>4.986150772144974</v>
+        <v>4.987014292843731</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3561578497294366</v>
+        <v>0.3552943290306798</v>
       </c>
       <c r="F147" t="n">
         <v>5.581807858149219</v>
       </c>
       <c r="G147" t="n">
-        <v>4.579826858033617</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -5953,22 +5953,22 @@
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>45776</v>
+        <v>45740</v>
       </c>
       <c r="C148" t="n">
         <v>5.342308621874411</v>
       </c>
       <c r="D148" t="n">
-        <v>4.987903302195027</v>
+        <v>4.981228991126805</v>
       </c>
       <c r="E148" t="n">
-        <v>0.3544053196793833</v>
+        <v>0.3610796307476054</v>
       </c>
       <c r="F148" t="n">
         <v>5.581807858149219</v>
       </c>
       <c r="G148" t="n">
-        <v>4.579826858033617</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
@@ -5986,22 +5986,22 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>45778</v>
+        <v>45747</v>
       </c>
       <c r="C149" t="n">
         <v>5.342308621874411</v>
       </c>
       <c r="D149" t="n">
-        <v>4.970216494093361</v>
+        <v>4.986150772144974</v>
       </c>
       <c r="E149" t="n">
-        <v>0.3720921277810501</v>
+        <v>0.3561578497294366</v>
       </c>
       <c r="F149" t="n">
         <v>5.581807858149219</v>
       </c>
       <c r="G149" t="n">
-        <v>4.579826858033617</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -6019,55 +6019,55 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>45817</v>
+        <v>45776</v>
       </c>
       <c r="C150" t="n">
+        <v>5.342308621874411</v>
+      </c>
+      <c r="D150" t="n">
+        <v>4.987903302195027</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.3544053196793833</v>
+      </c>
+      <c r="F150" t="n">
         <v>5.581807858149219</v>
       </c>
-      <c r="D150" t="n">
-        <v>4.982452195977958</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0.599355662171261</v>
-      </c>
-      <c r="F150" t="n">
-        <v>4.982452195977958</v>
-      </c>
       <c r="G150" t="n">
-        <v>4.579826858033617</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TREE US Equity</t>
+          <t>TOST US Equity</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>43609</v>
+        <v>45778</v>
       </c>
       <c r="C151" t="n">
-        <v>6.743392425454591</v>
+        <v>5.342308621874411</v>
       </c>
       <c r="D151" t="n">
-        <v>4.933845433903099</v>
+        <v>4.970216494093361</v>
       </c>
       <c r="E151" t="n">
-        <v>1.809546991551492</v>
+        <v>0.3720921277810501</v>
       </c>
       <c r="F151" t="n">
-        <v>5.503534374600851</v>
+        <v>5.581807858149219</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -6075,62 +6075,62 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>297</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TREE US Equity</t>
+          <t>TOST US Equity</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>43908</v>
+        <v>45817</v>
       </c>
       <c r="C152" t="n">
-        <v>6.743392425454591</v>
+        <v>5.581807858149219</v>
       </c>
       <c r="D152" t="n">
-        <v>4.420434451080995</v>
+        <v>4.982452195977958</v>
       </c>
       <c r="E152" t="n">
-        <v>2.322957974373596</v>
+        <v>0.599355662171261</v>
       </c>
       <c r="F152" t="n">
-        <v>4.952576892109302</v>
+        <v>4.982452195977958</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>3.706316784422607</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>428</v>
+        <v>123</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>TREE US Equity</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>44741</v>
+        <v>43609</v>
       </c>
       <c r="C153" t="n">
-        <v>8.598499657580531</v>
+        <v>6.743392425454591</v>
       </c>
       <c r="D153" t="n">
-        <v>4.292637559020869</v>
+        <v>4.933845433903099</v>
       </c>
       <c r="E153" t="n">
-        <v>4.305862098559662</v>
+        <v>1.809546991551492</v>
       </c>
       <c r="F153" t="n">
-        <v>8.106988459280267</v>
+        <v>5.503534374600851</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -6141,40 +6141,40 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>297</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TWLO US Equity</t>
+          <t>TREE US Equity</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>44872</v>
+        <v>43908</v>
       </c>
       <c r="C154" t="n">
-        <v>8.598499657580531</v>
+        <v>6.743392425454591</v>
       </c>
       <c r="D154" t="n">
-        <v>4.800950844809583</v>
+        <v>4.420434451080995</v>
       </c>
       <c r="E154" t="n">
-        <v>3.797548812770947</v>
+        <v>2.322957974373596</v>
       </c>
       <c r="F154" t="n">
-        <v>7.034561738608683</v>
+        <v>4.952576892109302</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>428</v>
       </c>
     </row>
     <row r="155">
@@ -6184,19 +6184,19 @@
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>45042</v>
+        <v>44741</v>
       </c>
       <c r="C155" t="n">
         <v>8.598499657580531</v>
       </c>
       <c r="D155" t="n">
-        <v>4.949813656295606</v>
+        <v>4.292637559020869</v>
       </c>
       <c r="E155" t="n">
-        <v>3.648686001284925</v>
+        <v>4.305862098559662</v>
       </c>
       <c r="F155" t="n">
-        <v>6.390010005103135</v>
+        <v>8.106988459280267</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -6217,129 +6217,129 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>45330</v>
+        <v>44872</v>
       </c>
       <c r="C156" t="n">
         <v>8.598499657580531</v>
       </c>
       <c r="D156" t="n">
-        <v>4.963755288063709</v>
+        <v>4.800950844809583</v>
       </c>
       <c r="E156" t="n">
-        <v>3.634744369516822</v>
+        <v>3.797548812770947</v>
       </c>
       <c r="F156" t="n">
-        <v>4.963755288063709</v>
+        <v>7.034561738608683</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>XYZ US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>45712</v>
+        <v>45042</v>
       </c>
       <c r="C157" t="n">
-        <v>13.84986353941615</v>
+        <v>8.598499657580531</v>
       </c>
       <c r="D157" t="n">
-        <v>4.575913189336205</v>
+        <v>4.949813656295606</v>
       </c>
       <c r="E157" t="n">
-        <v>9.273950350079943</v>
+        <v>3.648686001284925</v>
       </c>
       <c r="F157" t="n">
-        <v>4.70956642660217</v>
+        <v>6.390010005103135</v>
       </c>
       <c r="G157" t="n">
-        <v>3.242466314934898</v>
+        <v>0</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Still Residual</t>
+          <t>Recovered to Large</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>186</v>
+        <v>27</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Z US Equity</t>
+          <t>TWLO US Equity</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>43627</v>
+        <v>45330</v>
       </c>
       <c r="C158" t="n">
-        <v>5.463890354493641</v>
+        <v>8.598499657580531</v>
       </c>
       <c r="D158" t="n">
-        <v>4.650544258930033</v>
+        <v>4.963755288063709</v>
       </c>
       <c r="E158" t="n">
-        <v>0.8133460955636078</v>
+        <v>3.634744369516822</v>
       </c>
       <c r="F158" t="n">
-        <v>6.609626940393729</v>
+        <v>4.963755288063709</v>
       </c>
       <c r="G158" t="n">
-        <v>1.681352326847488</v>
+        <v>0</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Z US Equity</t>
+          <t>XYZ US Equity</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>43685</v>
+        <v>45712</v>
       </c>
       <c r="C159" t="n">
-        <v>5.463890354493641</v>
+        <v>13.84986353941615</v>
       </c>
       <c r="D159" t="n">
-        <v>4.355367857077193</v>
+        <v>4.575913189336205</v>
       </c>
       <c r="E159" t="n">
-        <v>1.108522497416448</v>
+        <v>9.273950350079943</v>
       </c>
       <c r="F159" t="n">
-        <v>6.609626940393729</v>
+        <v>4.70956642660217</v>
       </c>
       <c r="G159" t="n">
-        <v>1.681352326847488</v>
+        <v>3.017245113947369</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Recovered to Large</t>
+          <t>Still Residual</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>125</v>
+        <v>228</v>
       </c>
     </row>
     <row r="160">
@@ -6349,22 +6349,22 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>43811</v>
+        <v>43627</v>
       </c>
       <c r="C160" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D160" t="n">
-        <v>4.986297602587926</v>
+        <v>4.650544258930033</v>
       </c>
       <c r="E160" t="n">
-        <v>0.477592751905715</v>
+        <v>0.8133460955636078</v>
       </c>
       <c r="F160" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G160" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="161">
@@ -6382,22 +6382,22 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>43825</v>
+        <v>43685</v>
       </c>
       <c r="C161" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D161" t="n">
-        <v>4.608033927082164</v>
+        <v>4.355367857077193</v>
       </c>
       <c r="E161" t="n">
-        <v>0.855856427411477</v>
+        <v>1.108522497416448</v>
       </c>
       <c r="F161" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G161" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="162">
@@ -6415,22 +6415,22 @@
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>43963</v>
+        <v>43811</v>
       </c>
       <c r="C162" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D162" t="n">
-        <v>4.538726599393854</v>
+        <v>4.986297602587926</v>
       </c>
       <c r="E162" t="n">
-        <v>0.9251637550997867</v>
+        <v>0.477592751905715</v>
       </c>
       <c r="F162" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G162" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163">
@@ -6448,22 +6448,22 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>43979</v>
+        <v>43825</v>
       </c>
       <c r="C163" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D163" t="n">
-        <v>4.967190567942826</v>
+        <v>4.608033927082164</v>
       </c>
       <c r="E163" t="n">
-        <v>0.4966997865508151</v>
+        <v>0.855856427411477</v>
       </c>
       <c r="F163" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G163" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>6</v>
+        <v>137</v>
       </c>
     </row>
     <row r="164">
@@ -6481,22 +6481,22 @@
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>43987</v>
+        <v>43963</v>
       </c>
       <c r="C164" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D164" t="n">
-        <v>4.795040812454965</v>
+        <v>4.538726599393854</v>
       </c>
       <c r="E164" t="n">
-        <v>0.668849542038676</v>
+        <v>0.9251637550997867</v>
       </c>
       <c r="F164" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G164" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="165">
@@ -6514,22 +6514,22 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>43991</v>
+        <v>43979</v>
       </c>
       <c r="C165" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D165" t="n">
-        <v>4.906795583620527</v>
+        <v>4.967190567942826</v>
       </c>
       <c r="E165" t="n">
-        <v>0.557094770873114</v>
+        <v>0.4966997865508151</v>
       </c>
       <c r="F165" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G165" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166">
@@ -6547,22 +6547,22 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>44040</v>
+        <v>43987</v>
       </c>
       <c r="C166" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D166" t="n">
-        <v>4.903191662392849</v>
+        <v>4.795040812454965</v>
       </c>
       <c r="E166" t="n">
-        <v>0.5606986921007922</v>
+        <v>0.668849542038676</v>
       </c>
       <c r="F166" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G166" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
@@ -6580,22 +6580,22 @@
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>44043</v>
+        <v>43991</v>
       </c>
       <c r="C167" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D167" t="n">
-        <v>4.914890990386857</v>
+        <v>4.906795583620527</v>
       </c>
       <c r="E167" t="n">
-        <v>0.5489993641067841</v>
+        <v>0.557094770873114</v>
       </c>
       <c r="F167" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G167" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="168">
@@ -6613,22 +6613,22 @@
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>44054</v>
+        <v>44040</v>
       </c>
       <c r="C168" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D168" t="n">
-        <v>3.946431078068288</v>
+        <v>4.903191662392849</v>
       </c>
       <c r="E168" t="n">
-        <v>1.517459276425352</v>
+        <v>0.5606986921007922</v>
       </c>
       <c r="F168" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G168" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>184</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
@@ -6646,22 +6646,22 @@
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>44245</v>
+        <v>44043</v>
       </c>
       <c r="C169" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D169" t="n">
-        <v>4.893597895300918</v>
+        <v>4.914890990386857</v>
       </c>
       <c r="E169" t="n">
-        <v>0.5702924591927232</v>
+        <v>0.5489993641067841</v>
       </c>
       <c r="F169" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G169" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -6679,22 +6679,22 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>44267</v>
+        <v>44054</v>
       </c>
       <c r="C170" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D170" t="n">
-        <v>4.920595177821651</v>
+        <v>3.946431078068288</v>
       </c>
       <c r="E170" t="n">
-        <v>0.5432951766719896</v>
+        <v>1.517459276425352</v>
       </c>
       <c r="F170" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G170" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>138</v>
+        <v>184</v>
       </c>
     </row>
     <row r="171">
@@ -6712,22 +6712,22 @@
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>44406</v>
+        <v>44245</v>
       </c>
       <c r="C171" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D171" t="n">
-        <v>4.928293500870908</v>
+        <v>4.893597895300918</v>
       </c>
       <c r="E171" t="n">
-        <v>0.5355968536227325</v>
+        <v>0.5702924591927232</v>
       </c>
       <c r="F171" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G171" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172">
@@ -6745,22 +6745,22 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>44432</v>
+        <v>44267</v>
       </c>
       <c r="C172" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D172" t="n">
-        <v>4.962440569064522</v>
+        <v>4.920595177821651</v>
       </c>
       <c r="E172" t="n">
-        <v>0.5014497854291191</v>
+        <v>0.5432951766719896</v>
       </c>
       <c r="F172" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G172" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>138</v>
       </c>
     </row>
     <row r="173">
@@ -6778,22 +6778,22 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>44438</v>
+        <v>44406</v>
       </c>
       <c r="C173" t="n">
         <v>5.463890354493641</v>
       </c>
       <c r="D173" t="n">
-        <v>4.882695993893408</v>
+        <v>4.928293500870908</v>
       </c>
       <c r="E173" t="n">
-        <v>0.5811943606002332</v>
+        <v>0.5355968536227325</v>
       </c>
       <c r="F173" t="n">
         <v>6.609626940393729</v>
       </c>
       <c r="G173" t="n">
-        <v>1.681352326847488</v>
+        <v>1.297834673536594</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174">
@@ -6811,30 +6811,96 @@
         </is>
       </c>
       <c r="B174" s="2" t="n">
+        <v>44432</v>
+      </c>
+      <c r="C174" t="n">
+        <v>5.463890354493641</v>
+      </c>
+      <c r="D174" t="n">
+        <v>4.962440569064522</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.5014497854291191</v>
+      </c>
+      <c r="F174" t="n">
+        <v>6.609626940393729</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1.297834673536594</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Recovered to Large</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Z US Equity</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>44438</v>
+      </c>
+      <c r="C175" t="n">
+        <v>5.463890354493641</v>
+      </c>
+      <c r="D175" t="n">
+        <v>4.882695993893408</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.5811943606002332</v>
+      </c>
+      <c r="F175" t="n">
+        <v>6.609626940393729</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1.297834673536594</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Recovered to Large</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Z US Equity</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="n">
         <v>44504</v>
       </c>
-      <c r="C174" t="n">
+      <c r="C176" t="n">
         <v>6.609626940393729</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D176" t="n">
         <v>3.424450061324469</v>
       </c>
-      <c r="E174" t="n">
+      <c r="E176" t="n">
         <v>3.18517687906926</v>
       </c>
-      <c r="F174" t="n">
+      <c r="F176" t="n">
         <v>4.02375816608119</v>
       </c>
-      <c r="G174" t="n">
-        <v>1.681352326847488</v>
-      </c>
-      <c r="H174" t="inlineStr">
+      <c r="G176" t="n">
+        <v>1.297834673536594</v>
+      </c>
+      <c r="H176" t="inlineStr">
         <is>
           <t>Still Residual</t>
         </is>
       </c>
-      <c r="I174" t="n">
-        <v>1394</v>
+      <c r="I176" t="n">
+        <v>1436</v>
       </c>
     </row>
   </sheetData>
@@ -6848,7 +6914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6900,666 +6966,172 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAD Curncy</t>
+          <t>BABA US Equity</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>44111</v>
+        <v>44446</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>44235</v>
+        <v>45923</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>1477</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2632873394351858</v>
+        <v>0.5474875512866419</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>META US Equity</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43521</v>
+        <v>44558</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>43637</v>
+        <v>45281</v>
       </c>
       <c r="D4" t="n">
-        <v>116</v>
+        <v>723</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001964416139246338</v>
+        <v>0.5092618261890409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>NVDA US Equity</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43641</v>
+        <v>44334</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>43707</v>
+        <v>44708</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>374</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3878927770042555</v>
+        <v>0.4042329336493665</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>PINS US Equity</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>43713</v>
+        <v>44545</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>43951</v>
+        <v>44952</v>
       </c>
       <c r="D6" t="n">
-        <v>238</v>
+        <v>407</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001509179929640628</v>
+        <v>0.6843959624037065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>PLTR US Equity</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>43986</v>
+        <v>44620</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>44085</v>
+        <v>45064</v>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>444</v>
       </c>
       <c r="E7" t="n">
-        <v>7.238301190557532e-07</v>
+        <v>0.2560260324007131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>PYPL US Equity</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>44088</v>
+        <v>44610</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>44610</v>
+        <v>45436</v>
       </c>
       <c r="D8" t="n">
-        <v>522</v>
+        <v>826</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008251777708662412</v>
+        <v>0.6457146440286845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>SE US Equity</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>44614</v>
+        <v>44881</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>45336</v>
+        <v>45356</v>
       </c>
       <c r="D9" t="n">
-        <v>722</v>
+        <v>475</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1612095762656547</v>
+        <v>0.2505158017269435</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EUR Curncy</t>
+          <t>SHOP CN Equity</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45337</v>
+        <v>43900</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>45385</v>
+        <v>44132</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0001897852011505419</v>
+        <v>0.4834538818653537</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HKD Curncy</t>
+          <t>TWTR US Equity</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>44032</v>
+        <v>43773</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>44172</v>
+        <v>44531</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>758</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06757609380609853</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HKD Curncy</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>44372</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>44442</v>
-      </c>
-      <c r="D12" t="n">
-        <v>70</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.2130721935694165</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HKD Curncy</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>44446</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>45385</v>
-      </c>
-      <c r="D13" t="n">
-        <v>939</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-5.06221859042014e-07</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>43675</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>43810</v>
-      </c>
-      <c r="D14" t="n">
-        <v>135</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0142690742599815</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>43811</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>43894</v>
-      </c>
-      <c r="D15" t="n">
-        <v>83</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.011516593765187</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>43906</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>43971</v>
-      </c>
-      <c r="D16" t="n">
-        <v>65</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.09051575473033632</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>43991</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>44025</v>
-      </c>
-      <c r="D17" t="n">
-        <v>34</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.05187143232492531</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>44067</v>
-      </c>
-      <c r="D18" t="n">
-        <v>41</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.07743346053086182</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>44225</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>44266</v>
-      </c>
-      <c r="D19" t="n">
-        <v>41</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.01131133997354291</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>44298</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>44342</v>
-      </c>
-      <c r="D20" t="n">
-        <v>44</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.1330329822073394</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>44364</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>44610</v>
-      </c>
-      <c r="D21" t="n">
-        <v>246</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.002443742261310396</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>44630</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>44690</v>
-      </c>
-      <c r="D22" t="n">
-        <v>60</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.003012984095514021</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>44728</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>44778</v>
-      </c>
-      <c r="D23" t="n">
-        <v>50</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.001416672609090148</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>44781</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>44957</v>
-      </c>
-      <c r="D24" t="n">
-        <v>176</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.008081244977611568</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>44958</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>45079</v>
-      </c>
-      <c r="D25" t="n">
-        <v>121</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.01569686210095401</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45082</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>45282</v>
-      </c>
-      <c r="D26" t="n">
-        <v>200</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.2239422313308192</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>JPY Curncy</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45286</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>45357</v>
-      </c>
-      <c r="D27" t="n">
-        <v>71</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.5111178541361689</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>META US Equity</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>44558</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>45281</v>
-      </c>
-      <c r="D28" t="n">
-        <v>723</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.5092618261890409</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NVDA US Equity</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>44334</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>44708</v>
-      </c>
-      <c r="D29" t="n">
-        <v>374</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.4042329336493665</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PINS US Equity</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>44545</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>44952</v>
-      </c>
-      <c r="D30" t="n">
-        <v>407</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.6843959624037065</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PLTR US Equity</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>44620</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>45064</v>
-      </c>
-      <c r="D31" t="n">
-        <v>444</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.2560260324007131</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>PYPL US Equity</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>44610</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>45436</v>
-      </c>
-      <c r="D32" t="n">
-        <v>826</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.6457146440286845</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SE US Equity</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>44881</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>45356</v>
-      </c>
-      <c r="D33" t="n">
-        <v>475</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.2505158017269435</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SHOP CN Equity</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>43900</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>44132</v>
-      </c>
-      <c r="D34" t="n">
-        <v>232</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.4834538818653537</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TWTR US Equity</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>43773</v>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>44531</v>
-      </c>
-      <c r="D35" t="n">
-        <v>758</v>
-      </c>
-      <c r="E35" t="n">
         <v>0.5063608440363557</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ZAR Curncy</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>44959</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>45215</v>
-      </c>
-      <c r="D36" t="n">
-        <v>256</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02232509365285203</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ZAR Curncy</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45216</v>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>45385</v>
-      </c>
-      <c r="D37" t="n">
-        <v>169</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.0003329798795747985</v>
       </c>
     </row>
   </sheetData>
